--- a/TeDoen.xlsx
+++ b/TeDoen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qduys\OneDrive\Bureaublad\ma\GitHub\BO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3F328E-578A-4750-BE16-FE509EF9D0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB56A18-39AF-4B08-84E6-539B50D6A300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
   <si>
     <t>Page</t>
   </si>
@@ -764,7 +764,7 @@
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="9.21875" customWidth="1"/>
     <col min="8" max="8" width="8.21875" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" customWidth="1"/>
     <col min="10" max="10" width="12.109375" customWidth="1"/>
     <col min="11" max="11" width="17.88671875" customWidth="1"/>
     <col min="12" max="12" width="17.5546875" customWidth="1"/>
@@ -2076,9 +2076,7 @@
         <v>24</v>
       </c>
       <c r="E19" s="8"/>
-      <c r="F19" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="7" t="s">
@@ -2268,7 +2266,9 @@
       <c r="B22" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="7"/>
+      <c r="C22" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -2333,7 +2333,9 @@
       <c r="B23" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="7"/>
+      <c r="C23" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -2398,7 +2400,9 @@
       <c r="B24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="7"/>
+      <c r="C24" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -2463,7 +2467,9 @@
       <c r="B25" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="7"/>
+      <c r="C25" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -2528,7 +2534,9 @@
       <c r="B26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="7"/>
+      <c r="C26" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -2593,7 +2601,9 @@
       <c r="B27" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="7"/>
+      <c r="C27" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>

--- a/TeDoen.xlsx
+++ b/TeDoen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qduys\OneDrive\Bureaublad\ma\GitHub\BO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB56A18-39AF-4B08-84E6-539B50D6A300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45E8B5C-BEA6-48E2-A932-D38AB3578944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="76">
   <si>
     <t>Page</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>Information about</t>
+  </si>
+  <si>
+    <t>privicy policy</t>
+  </si>
+  <si>
+    <t>From</t>
   </si>
 </sst>
 </file>
@@ -767,7 +773,7 @@
     <col min="9" max="9" width="20.21875" customWidth="1"/>
     <col min="10" max="10" width="12.109375" customWidth="1"/>
     <col min="11" max="11" width="17.88671875" customWidth="1"/>
-    <col min="12" max="12" width="17.5546875" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
     <col min="13" max="13" width="26.109375" style="4" customWidth="1"/>
     <col min="14" max="14" width="20.33203125" customWidth="1"/>
     <col min="15" max="15" width="23.109375" customWidth="1"/>
@@ -1481,7 +1487,9 @@
       <c r="R11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="S11" s="5"/>
+      <c r="S11" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
@@ -1561,10 +1569,10 @@
       <c r="Q12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="7"/>
+      <c r="S12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
@@ -1647,7 +1655,9 @@
       <c r="R13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="S13" s="5"/>
+      <c r="S13" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
@@ -1719,16 +1729,14 @@
         <v>55</v>
       </c>
       <c r="O14" s="7"/>
-      <c r="P14" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="P14" s="7"/>
       <c r="Q14" s="7" t="s">
         <v>62</v>
       </c>
       <c r="R14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="S14" s="5"/>
+      <c r="S14" s="7"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
@@ -1803,7 +1811,7 @@
       <c r="R15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="S15" s="5"/>
+      <c r="S15" s="7"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -1876,7 +1884,7 @@
       <c r="R16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="S16" s="5"/>
+      <c r="S16" s="7"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
@@ -1949,7 +1957,7 @@
       <c r="R17" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="S17" s="5"/>
+      <c r="S17" s="7"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -2022,7 +2030,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
-      <c r="S18" s="5"/>
+      <c r="S18" s="7"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
@@ -2093,7 +2101,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
-      <c r="S19" s="5"/>
+      <c r="S19" s="7"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
@@ -2154,7 +2162,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
-      <c r="S20" s="5"/>
+      <c r="S20" s="7"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
@@ -2219,7 +2227,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="5"/>
+      <c r="S21" s="7"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
@@ -2286,7 +2294,7 @@
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
-      <c r="S22" s="5"/>
+      <c r="S22" s="7"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
@@ -3931,7 +3939,7 @@
     <row r="47" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="7" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>71</v>

--- a/TeDoen.xlsx
+++ b/TeDoen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qduys\OneDrive\Bureaublad\ma\GitHub\BO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45E8B5C-BEA6-48E2-A932-D38AB3578944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2AD82E-D1B7-4E0D-8B6D-09414F80F338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{7461CF4B-3121-403A-BC5A-7F9623395FEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="74">
   <si>
     <t>Page</t>
   </si>
@@ -167,9 +167,6 @@
     <t xml:space="preserve">reviews </t>
   </si>
   <si>
-    <t>The team</t>
-  </si>
-  <si>
     <t>To eat &amp; drink</t>
   </si>
   <si>
@@ -254,16 +251,13 @@
     <t>s</t>
   </si>
   <si>
-    <t>the museum</t>
-  </si>
-  <si>
-    <t>Information about</t>
-  </si>
-  <si>
     <t>privicy policy</t>
   </si>
   <si>
     <t>From</t>
+  </si>
+  <si>
+    <t>ons team</t>
   </si>
 </sst>
 </file>
@@ -336,7 +330,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -376,19 +370,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -406,9 +387,25 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -437,15 +434,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,13 +769,13 @@
     <col min="8" max="8" width="8.21875" customWidth="1"/>
     <col min="9" max="9" width="20.21875" customWidth="1"/>
     <col min="10" max="10" width="12.109375" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="20.88671875" customWidth="1"/>
+    <col min="12" max="12" width="30.44140625" customWidth="1"/>
+    <col min="13" max="13" width="29.44140625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="22.44140625" customWidth="1"/>
     <col min="15" max="15" width="23.109375" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="16" max="16" width="16.21875" customWidth="1"/>
+    <col min="17" max="17" width="20.5546875" customWidth="1"/>
     <col min="18" max="18" width="19.109375" customWidth="1"/>
     <col min="19" max="19" width="24.77734375" customWidth="1"/>
     <col min="20" max="20" width="13.77734375" customWidth="1"/>
@@ -1394,7 +1391,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
@@ -1466,30 +1463,28 @@
       <c r="K11" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>6</v>
+      <c r="L11" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R11" s="11" t="s">
+      <c r="Q11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="S11" s="13" t="s">
-        <v>59</v>
-      </c>
+      <c r="R11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="S11" s="20"/>
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
@@ -1534,12 +1529,14 @@
     <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -1548,31 +1545,31 @@
         <v>35</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>44</v>
+      <c r="L12" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S12" s="20"/>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
@@ -1617,7 +1614,7 @@
     <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>18</v>
@@ -1628,36 +1625,34 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="19" t="s">
-        <v>72</v>
+      <c r="L13" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>57</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>75</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="S13" s="20"/>
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
@@ -1702,7 +1697,7 @@
     <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>18</v>
@@ -1720,23 +1715,21 @@
         <v>40</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="Q14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="S14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="20"/>
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
@@ -1781,7 +1774,7 @@
     <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>18</v>
@@ -1798,20 +1791,20 @@
       <c r="K15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="L15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="Q15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="R15" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="S15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="20"/>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
@@ -1856,7 +1849,7 @@
     <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>18</v>
@@ -1873,18 +1866,18 @@
       <c r="K16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="L16" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="7"/>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7" t="s">
+      <c r="Q16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="S16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="20"/>
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
@@ -1929,35 +1922,39 @@
     <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7" t="s">
-        <v>50</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="7"/>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="S17" s="7"/>
+      <c r="Q17" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="R17" s="7"/>
+      <c r="S17" s="20"/>
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -2002,7 +1999,7 @@
     <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>25</v>
@@ -2011,9 +2008,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="7" t="s">
@@ -2021,16 +2016,18 @@
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="L18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="7"/>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
       <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
+      <c r="Q18" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
+      <c r="S18" s="20"/>
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
@@ -2074,34 +2071,24 @@
     </row>
     <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
-      <c r="B19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="16"/>
       <c r="J19" s="5"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="M19" s="7"/>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
+      <c r="S19" s="20"/>
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
@@ -2143,16 +2130,20 @@
       <c r="BF19" s="1"/>
       <c r="BG19" s="1"/>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="18"/>
+      <c r="B20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="7"/>
       <c r="J20" s="5"/>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2162,7 +2153,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
+      <c r="S20" s="20"/>
       <c r="T20" s="5"/>
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
@@ -2204,20 +2195,22 @@
       <c r="BF20" s="1"/>
       <c r="BG20" s="1"/>
     </row>
-    <row r="21" spans="1:59" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2227,7 +2220,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
+      <c r="S21" s="20"/>
       <c r="T21" s="5"/>
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
@@ -2272,10 +2265,10 @@
     <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -2294,7 +2287,7 @@
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
+      <c r="S22" s="20"/>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
@@ -2344,13 +2337,15 @@
       <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="7"/>
+      <c r="D23" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2411,7 +2406,9 @@
       <c r="C24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="7"/>
+      <c r="D24" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -2476,9 +2473,11 @@
         <v>66</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -2543,7 +2542,7 @@
         <v>67</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -2551,7 +2550,7 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -2607,18 +2606,20 @@
     <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="D27" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
       <c r="I27" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2941,7 +2942,9 @@
       <c r="C32" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="8"/>
+      <c r="D32" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8" t="s">
@@ -3005,12 +3008,14 @@
     <row r="33" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="8"/>
+      <c r="D33" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -3072,7 +3077,7 @@
     <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>25</v>
@@ -3083,7 +3088,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -3139,7 +3144,7 @@
     <row r="35" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>25</v>
@@ -3206,7 +3211,7 @@
     <row r="36" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>25</v>
@@ -3273,7 +3278,7 @@
     <row r="37" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>25</v>
@@ -3340,18 +3345,22 @@
     <row r="38" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
+      <c r="F38" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
       <c r="I38" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -3407,12 +3416,14 @@
     <row r="39" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="8"/>
+      <c r="D39" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8" t="s">
         <v>29</v>
@@ -3475,22 +3486,14 @@
     </row>
     <row r="40" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
-      <c r="B40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="B40" s="15"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="16"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -3542,16 +3545,20 @@
       <c r="BF40" s="1"/>
       <c r="BG40" s="1"/>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:59" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="18"/>
+      <c r="B41" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="7"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
@@ -3603,20 +3610,22 @@
       <c r="BF41" s="1"/>
       <c r="BG41" s="1"/>
     </row>
-    <row r="42" spans="1:59" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
-      <c r="B42" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="7"/>
+      <c r="B42" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
@@ -3671,7 +3680,7 @@
     <row r="43" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>70</v>
@@ -3741,15 +3750,17 @@
         <v>64</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
       <c r="I44" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -3808,7 +3819,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -3872,12 +3883,14 @@
     <row r="46" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -3939,10 +3952,10 @@
     <row r="47" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -3950,7 +3963,7 @@
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
       <c r="I47" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -4006,18 +4019,20 @@
     <row r="48" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
       <c r="I48" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -4072,14 +4087,14 @@
     </row>
     <row r="49" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
@@ -4198,7 +4213,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="21"/>
+      <c r="F51" s="18"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -13304,10 +13319,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24:H24 D22:H23 E30 D24 F31:F41 D9:H20 H1:L2 F43:F48 G31:H48 D31:E48 H50:L1048576" xr:uid="{E98C5C63-1384-46F2-948D-015007CE5E74}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F23:H23 D21:H22 E30 D23 H1:L2 F42:F47 H50:L1048576 F33:F40 D9:H19 D33:E47 G33:H47 D48:H48 D31:H32 E27:H27" xr:uid="{E98C5C63-1384-46F2-948D-015007CE5E74}">
       <formula1>$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2 C9:C24 C31:C48 G50:G1048576" xr:uid="{D953101C-11E6-4395-8B7B-9F74007EFAE2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G2 G50:G1048576 C27 C9:C23 C31:C48" xr:uid="{D953101C-11E6-4395-8B7B-9F74007EFAE2}">
       <formula1>$F$2:$F$4</formula1>
     </dataValidation>
   </dataValidations>
